--- a/public/planilhas/06_cockpit_produtividade.xlsx
+++ b/public/planilhas/06_cockpit_produtividade.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BURNDOWN" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'DASHBOARD'!$A$1:$L$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'DASHBOARD'!$A$1:$R$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,12 +20,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="dd/mm"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="#,##0;(#,##0);&quot;—&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;(#,##0.0);&quot;—&quot;"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -141,6 +143,37 @@
       <color rgb="00C99C66"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="008A9691"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="00C99C66"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <color rgb="008A9691"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="0043D07F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="008A9691"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="0043D07F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -191,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -237,7 +270,21 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="20" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="18" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="24" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -246,7 +293,23 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <name val="Aptos Narrow"/>
+        <b val="1"/>
+        <color rgb="0043D07F"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Aptos Narrow"/>
+        <b val="1"/>
+        <color rgb="00D9534F"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <name val="Aptos Narrow"/>
@@ -393,6 +456,219 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Cascata · backlog → carga</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!C21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$B$22:$B$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$C$22:$C$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!D21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2E9E5B"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$B$22:$B$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$D$22:$D$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!E21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="D9534F"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$B$22:$B$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$E$22:$E$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!O21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="15000">
+              <a:solidFill>
+                <a:srgbClr val="C99C66"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$N$22:$N$28</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$O$22:$O$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
@@ -531,6 +807,50 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3960000" cy="2340000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3600000" cy="1440000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -855,7 +1175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:Z55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -977,27 +1297,27 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="2" t="n"/>
       <c r="B6" s="7">
-        <f>B40</f>
+        <f>Z40</f>
         <v/>
       </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="8">
-        <f>B41</f>
+        <f>Z41</f>
         <v/>
       </c>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="9">
-        <f>B42</f>
+        <f>Z42</f>
         <v/>
       </c>
       <c r="G6" s="6" t="n"/>
       <c r="H6" s="10">
-        <f>B43</f>
+        <f>Z43</f>
         <v/>
       </c>
       <c r="I6" s="6" t="n"/>
       <c r="J6" s="11">
-        <f>B45</f>
+        <f>Z45</f>
         <v/>
       </c>
       <c r="K6" s="6" t="n"/>
@@ -1042,7 +1362,7 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="2" t="n"/>
       <c r="B9" s="13">
-        <f>IF(B41&gt;3,"🟠 WIP acima do limite — termine antes de começar novas.",IF(B45&gt;0,"🔴 Há tarefas envelhecidas/alta paradas — priorize hoje.","🟢 Fluxo saudável. Mantenha o ritmo."))</f>
+        <f>IF(Z41&gt;3,"🟠 WIP acima do limite — termine antes de começar novas.",IF(Z45&gt;0,"🔴 Há tarefas envelhecidas/alta paradas — priorize hoje.","🟢 Fluxo saudável. Mantenha o ritmo."))</f>
         <v/>
       </c>
       <c r="C9" s="14" t="n"/>
@@ -1231,7 +1551,11 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Cascata do fluxo</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
@@ -1242,76 +1566,246 @@
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
-    </row>
-    <row r="21">
+      <c r="N20" s="19" t="inlineStr">
+        <is>
+          <t>Spark · burndown real</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
       <c r="A21" s="2" t="n"/>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Etapa</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="G21" s="16" t="inlineStr">
+        <is>
+          <t>Δ</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
+      <c r="N21" s="16" t="inlineStr">
+        <is>
+          <t>Ponto</t>
+        </is>
+      </c>
+      <c r="O21" s="16" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="P21" s="20" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Backlog (a fazer)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="21">
+        <f>IF(G22&gt;=0,G22,0)</f>
+        <v/>
+      </c>
+      <c r="E22" s="21">
+        <f>IF(G22&lt;0,-G22,0)</f>
+        <v/>
+      </c>
+      <c r="F22" s="21">
+        <f>G22</f>
+        <v/>
+      </c>
+      <c r="G22" s="22">
+        <f>$Z$40</f>
+        <v/>
+      </c>
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
+      <c r="N22" s="23" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="O22" s="24">
+        <f>BURNDOWN!C6</f>
+        <v/>
+      </c>
+      <c r="P22" s="25">
+        <f>IF(OR(O22="",NOT(ISNUMBER(O22))),"",REPT("▬",MAX(1,ROUND((O22-(MIN(O22:O28)))/MAX(1E-9,(MAX(O22:O28))-(MIN(O22:O28)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>+ Em andamento</t>
+        </is>
+      </c>
+      <c r="C23" s="21">
+        <f>IF(G23&gt;=0,F22,F22+G23)</f>
+        <v/>
+      </c>
+      <c r="D23" s="21">
+        <f>IF(G23&gt;=0,G23,0)</f>
+        <v/>
+      </c>
+      <c r="E23" s="21">
+        <f>IF(G23&lt;0,-G23,0)</f>
+        <v/>
+      </c>
+      <c r="F23" s="21">
+        <f>F22+G23</f>
+        <v/>
+      </c>
+      <c r="G23" s="22">
+        <f>$Z$41</f>
+        <v/>
+      </c>
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="n"/>
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
+      <c r="N23" s="23" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="O23" s="24">
+        <f>BURNDOWN!C7</f>
+        <v/>
+      </c>
+      <c r="P23" s="25">
+        <f>IF(OR(O23="",NOT(ISNUMBER(O23))),"",REPT("▬",MAX(1,ROUND((O23-(MIN(O22:O28)))/MAX(1E-9,(MAX(O22:O28))-(MIN(O22:O28)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n"/>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>− Concluídas</t>
+        </is>
+      </c>
+      <c r="C24" s="21">
+        <f>IF(G24&gt;=0,F23,F23+G24)</f>
+        <v/>
+      </c>
+      <c r="D24" s="21">
+        <f>IF(G24&gt;=0,G24,0)</f>
+        <v/>
+      </c>
+      <c r="E24" s="21">
+        <f>IF(G24&lt;0,-G24,0)</f>
+        <v/>
+      </c>
+      <c r="F24" s="21">
+        <f>F23+G24</f>
+        <v/>
+      </c>
+      <c r="G24" s="22">
+        <f>-$Z$42</f>
+        <v/>
+      </c>
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="n"/>
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
+      <c r="N24" s="23" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="O24" s="24">
+        <f>BURNDOWN!C8</f>
+        <v/>
+      </c>
+      <c r="P24" s="25">
+        <f>IF(OR(O24="",NOT(ISNUMBER(O24))),"",REPT("▬",MAX(1,ROUND((O24-(MIN(O22:O28)))/MAX(1E-9,(MAX(O22:O28))-(MIN(O22:O28)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>Carga líquida</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="21">
+        <f>IF(G25&gt;=0,G25,0)</f>
+        <v/>
+      </c>
+      <c r="E25" s="21">
+        <f>IF(G25&lt;0,-G25,0)</f>
+        <v/>
+      </c>
+      <c r="F25" s="21">
+        <f>G25</f>
+        <v/>
+      </c>
+      <c r="G25" s="22">
+        <f>$Z$40+$Z$41-$Z$42</f>
+        <v/>
+      </c>
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="n"/>
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
+      <c r="N25" s="23" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="O25" s="24">
+        <f>BURNDOWN!C9</f>
+        <v/>
+      </c>
+      <c r="P25" s="25">
+        <f>IF(OR(O25="",NOT(ISNUMBER(O25))),"",REPT("▬",MAX(1,ROUND((O25-(MIN(O22:O28)))/MAX(1E-9,(MAX(O22:O28))-(MIN(O22:O28)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -1326,6 +1820,19 @@
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
+      <c r="N26" s="23" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="O26" s="24">
+        <f>BURNDOWN!C10</f>
+        <v/>
+      </c>
+      <c r="P26" s="25">
+        <f>IF(OR(O26="",NOT(ISNUMBER(O26))),"",REPT("▬",MAX(1,ROUND((O26-(MIN(O22:O28)))/MAX(1E-9,(MAX(O22:O28))-(MIN(O22:O28)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -1340,6 +1847,19 @@
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
+      <c r="N27" s="23" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="O27" s="24">
+        <f>BURNDOWN!C11</f>
+        <v/>
+      </c>
+      <c r="P27" s="25">
+        <f>IF(OR(O27="",NOT(ISNUMBER(O27))),"",REPT("▬",MAX(1,ROUND((O27-(MIN(O22:O28)))/MAX(1E-9,(MAX(O22:O28))-(MIN(O22:O28)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -1354,6 +1874,19 @@
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
+      <c r="N28" s="23" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="O28" s="24">
+        <f>BURNDOWN!C12</f>
+        <v/>
+      </c>
+      <c r="P28" s="25">
+        <f>IF(OR(O28="",NOT(ISNUMBER(O28))),"",REPT("▬",MAX(1,ROUND((O28-(MIN(O22:O28)))/MAX(1E-9,(MAX(O22:O28))-(MIN(O22:O28)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -1371,7 +1904,11 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>MINI-SPARKLINES</t>
+        </is>
+      </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
@@ -1383,59 +1920,164 @@
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" ht="26" customHeight="1">
       <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Atual</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="H31" s="16" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>WIP</t>
+        </is>
+      </c>
+      <c r="C32" s="26">
+        <f>$Z$41</f>
+        <v/>
+      </c>
+      <c r="D32" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" s="27">
+        <f>$Z$41</f>
+        <v/>
+      </c>
+      <c r="J32" s="28">
+        <f>IF(D32=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((D32-(MIN(D32:I32)))/MAX(1E-9,(MAX(D32:I32))-(MIN(D32:I32)))*7+1,0))),1))&amp;IF(E32=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((E32-(MIN(D32:I32)))/MAX(1E-9,(MAX(D32:I32))-(MIN(D32:I32)))*7+1,0))),1))&amp;IF(F32=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((F32-(MIN(D32:I32)))/MAX(1E-9,(MAX(D32:I32))-(MIN(D32:I32)))*7+1,0))),1))&amp;IF(G32=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((G32-(MIN(D32:I32)))/MAX(1E-9,(MAX(D32:I32))-(MIN(D32:I32)))*7+1,0))),1))&amp;IF(H32=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((H32-(MIN(D32:I32)))/MAX(1E-9,(MAX(D32:I32))-(MIN(D32:I32)))*7+1,0))),1))&amp;IF(I32=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((I32-(MIN(D32:I32)))/MAX(1E-9,(MAX(D32:I32))-(MIN(D32:I32)))*7+1,0))),1))</f>
+        <v/>
+      </c>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
-      <c r="J33" s="2" t="n"/>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>Cycle time</t>
+        </is>
+      </c>
+      <c r="C33" s="26">
+        <f>$Z$43</f>
+        <v/>
+      </c>
+      <c r="D33" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E33" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" s="27" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G33" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="H33" s="27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I33" s="27">
+        <f>$Z$43</f>
+        <v/>
+      </c>
+      <c r="J33" s="28">
+        <f>IF(D33=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((D33-(MIN(D33:I33)))/MAX(1E-9,(MAX(D33:I33))-(MIN(D33:I33)))*7+1,0))),1))&amp;IF(E33=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((E33-(MIN(D33:I33)))/MAX(1E-9,(MAX(D33:I33))-(MIN(D33:I33)))*7+1,0))),1))&amp;IF(F33=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((F33-(MIN(D33:I33)))/MAX(1E-9,(MAX(D33:I33))-(MIN(D33:I33)))*7+1,0))),1))&amp;IF(G33=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((G33-(MIN(D33:I33)))/MAX(1E-9,(MAX(D33:I33))-(MIN(D33:I33)))*7+1,0))),1))&amp;IF(H33=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((H33-(MIN(D33:I33)))/MAX(1E-9,(MAX(D33:I33))-(MIN(D33:I33)))*7+1,0))),1))&amp;IF(I33=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((I33-(MIN(D33:I33)))/MAX(1E-9,(MAX(D33:I33))-(MIN(D33:I33)))*7+1,0))),1))</f>
+        <v/>
+      </c>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="n"/>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>Alertas</t>
+        </is>
+      </c>
+      <c r="C34" s="26">
+        <f>$Z$45</f>
+        <v/>
+      </c>
+      <c r="D34" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" s="27">
+        <f>$Z$45</f>
+        <v/>
+      </c>
+      <c r="J34" s="28">
+        <f>IF(D34=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((D34-(MIN(D34:I34)))/MAX(1E-9,(MAX(D34:I34))-(MIN(D34:I34)))*7+1,0))),1))&amp;IF(E34=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((E34-(MIN(D34:I34)))/MAX(1E-9,(MAX(D34:I34))-(MIN(D34:I34)))*7+1,0))),1))&amp;IF(F34=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((F34-(MIN(D34:I34)))/MAX(1E-9,(MAX(D34:I34))-(MIN(D34:I34)))*7+1,0))),1))&amp;IF(G34=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((G34-(MIN(D34:I34)))/MAX(1E-9,(MAX(D34:I34))-(MIN(D34:I34)))*7+1,0))),1))&amp;IF(H34=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((H34-(MIN(D34:I34)))/MAX(1E-9,(MAX(D34:I34))-(MIN(D34:I34)))*7+1,0))),1))&amp;IF(I34=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((I34-(MIN(D34:I34)))/MAX(1E-9,(MAX(D34:I34))-(MIN(D34:I34)))*7+1,0))),1))</f>
+        <v/>
+      </c>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
     </row>
@@ -1511,10 +2153,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
-      <c r="B40" s="19">
-        <f>COUNTIF(TAREFAS!D:D,"A fazer")</f>
-        <v/>
-      </c>
+      <c r="B40" s="2" t="n"/>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="n"/>
@@ -1525,13 +2164,14 @@
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
+      <c r="Z40" s="29">
+        <f>COUNTIF(TAREFAS!D:D,"A fazer")</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
-      <c r="B41" s="19">
-        <f>COUNTIF(TAREFAS!D:D,"Fazendo")</f>
-        <v/>
-      </c>
+      <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n"/>
       <c r="E41" s="2" t="n"/>
@@ -1542,13 +2182,14 @@
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="n"/>
+      <c r="Z41" s="29">
+        <f>COUNTIF(TAREFAS!D:D,"Fazendo")</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
-      <c r="B42" s="19">
-        <f>COUNTIF(TAREFAS!D:D,"Feito")</f>
-        <v/>
-      </c>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="n"/>
@@ -1559,13 +2200,14 @@
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
+      <c r="Z42" s="29">
+        <f>COUNTIF(TAREFAS!D:D,"Feito")</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
-      <c r="B43" s="19">
-        <f>IFERROR(AVERAGE(TAREFAS!G6:G156),0)</f>
-        <v/>
-      </c>
+      <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n"/>
       <c r="E43" s="2" t="n"/>
@@ -1576,13 +2218,14 @@
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
+      <c r="Z43" s="29">
+        <f>IFERROR(AVERAGE(TAREFAS!G6:G156),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
-      <c r="B44" s="19">
-        <f>COUNTIF(TAREFAS!I6:I156,"⚠*")+SUMPRODUCT(--ISNUMBER(SEARCH("⚠",TAREFAS!I6:I156)))*0</f>
-        <v/>
-      </c>
+      <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n"/>
@@ -1593,13 +2236,14 @@
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
+      <c r="Z44" s="29">
+        <f>COUNTIF(TAREFAS!I6:I156,"⚠*")+SUMPRODUCT(--ISNUMBER(SEARCH("⚠",TAREFAS!I6:I156)))*0</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
-      <c r="B45" s="19">
-        <f>SUMPRODUCT(--ISNUMBER(SEARCH("⚠",TAREFAS!I6:I156)))</f>
-        <v/>
-      </c>
+      <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n"/>
       <c r="E45" s="2" t="n"/>
@@ -1610,6 +2254,10 @@
       <c r="J45" s="2" t="n"/>
       <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="n"/>
+      <c r="Z45" s="29">
+        <f>SUMPRODUCT(--ISNUMBER(SEARCH("⚠",TAREFAS!I6:I156)))</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -1773,6 +2421,23 @@
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="H5:I5"/>
   </mergeCells>
+  <conditionalFormatting sqref="G22:G25">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C32:C34">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00C99C66"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1938,10 +2603,10 @@
           <t>Fazendo</t>
         </is>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="30" t="n">
         <v>46220</v>
       </c>
-      <c r="F6" s="20" t="n"/>
+      <c r="F6" s="30" t="n"/>
       <c r="G6" s="17">
         <f>IF(AND(D6="Feito",E6&lt;&gt;"",F6&lt;&gt;""),F6-E6,"")</f>
         <v/>
@@ -1979,10 +2644,10 @@
           <t>A fazer</t>
         </is>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="30" t="n">
         <v>46223</v>
       </c>
-      <c r="F7" s="20" t="n"/>
+      <c r="F7" s="30" t="n"/>
       <c r="G7" s="17">
         <f>IF(AND(D7="Feito",E7&lt;&gt;"",F7&lt;&gt;""),F7-E7,"")</f>
         <v/>
@@ -2020,10 +2685,10 @@
           <t>A fazer</t>
         </is>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="30" t="n">
         <v>46224</v>
       </c>
-      <c r="F8" s="20" t="n"/>
+      <c r="F8" s="30" t="n"/>
       <c r="G8" s="17">
         <f>IF(AND(D8="Feito",E8&lt;&gt;"",F8&lt;&gt;""),F8-E8,"")</f>
         <v/>
@@ -2061,10 +2726,10 @@
           <t>Fazendo</t>
         </is>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="30" t="n">
         <v>46221</v>
       </c>
-      <c r="F9" s="20" t="n"/>
+      <c r="F9" s="30" t="n"/>
       <c r="G9" s="17">
         <f>IF(AND(D9="Feito",E9&lt;&gt;"",F9&lt;&gt;""),F9-E9,"")</f>
         <v/>
@@ -2102,10 +2767,10 @@
           <t>Feito</t>
         </is>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="30" t="n">
         <v>46217</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="30" t="n">
         <v>46223</v>
       </c>
       <c r="G10" s="17">
@@ -2145,10 +2810,10 @@
           <t>A fazer</t>
         </is>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="30" t="n">
         <v>46225</v>
       </c>
-      <c r="F11" s="20" t="n"/>
+      <c r="F11" s="30" t="n"/>
       <c r="G11" s="17">
         <f>IF(AND(D11="Feito",E11&lt;&gt;"",F11&lt;&gt;""),F11-E11,"")</f>
         <v/>
@@ -2186,10 +2851,10 @@
           <t>Fazendo</t>
         </is>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="30" t="n">
         <v>46222</v>
       </c>
-      <c r="F12" s="20" t="n"/>
+      <c r="F12" s="30" t="n"/>
       <c r="G12" s="17">
         <f>IF(AND(D12="Feito",E12&lt;&gt;"",F12&lt;&gt;""),F12-E12,"")</f>
         <v/>
@@ -2227,10 +2892,10 @@
           <t>Feito</t>
         </is>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="30" t="n">
         <v>46215</v>
       </c>
-      <c r="F13" s="20" t="n">
+      <c r="F13" s="30" t="n">
         <v>46220</v>
       </c>
       <c r="G13" s="17">
@@ -2270,10 +2935,10 @@
           <t>A fazer</t>
         </is>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="30" t="n">
         <v>46224</v>
       </c>
-      <c r="F14" s="20" t="n"/>
+      <c r="F14" s="30" t="n"/>
       <c r="G14" s="17">
         <f>IF(AND(D14="Feito",E14&lt;&gt;"",F14&lt;&gt;""),F14-E14,"")</f>
         <v/>
@@ -2295,8 +2960,8 @@
       <c r="B15" s="17" t="n"/>
       <c r="C15" s="17" t="n"/>
       <c r="D15" s="17" t="n"/>
-      <c r="E15" s="20" t="n"/>
-      <c r="F15" s="20" t="n"/>
+      <c r="E15" s="30" t="n"/>
+      <c r="F15" s="30" t="n"/>
       <c r="G15" s="17">
         <f>IF(AND(D15="Feito",E15&lt;&gt;"",F15&lt;&gt;""),F15-E15,"")</f>
         <v/>
@@ -2318,8 +2983,8 @@
       <c r="B16" s="17" t="n"/>
       <c r="C16" s="17" t="n"/>
       <c r="D16" s="17" t="n"/>
-      <c r="E16" s="20" t="n"/>
-      <c r="F16" s="20" t="n"/>
+      <c r="E16" s="30" t="n"/>
+      <c r="F16" s="30" t="n"/>
       <c r="G16" s="17">
         <f>IF(AND(D16="Feito",E16&lt;&gt;"",F16&lt;&gt;""),F16-E16,"")</f>
         <v/>
@@ -2341,8 +3006,8 @@
       <c r="B17" s="17" t="n"/>
       <c r="C17" s="17" t="n"/>
       <c r="D17" s="17" t="n"/>
-      <c r="E17" s="20" t="n"/>
-      <c r="F17" s="20" t="n"/>
+      <c r="E17" s="30" t="n"/>
+      <c r="F17" s="30" t="n"/>
       <c r="G17" s="17">
         <f>IF(AND(D17="Feito",E17&lt;&gt;"",F17&lt;&gt;""),F17-E17,"")</f>
         <v/>
@@ -2364,8 +3029,8 @@
       <c r="B18" s="17" t="n"/>
       <c r="C18" s="17" t="n"/>
       <c r="D18" s="17" t="n"/>
-      <c r="E18" s="20" t="n"/>
-      <c r="F18" s="20" t="n"/>
+      <c r="E18" s="30" t="n"/>
+      <c r="F18" s="30" t="n"/>
       <c r="G18" s="17">
         <f>IF(AND(D18="Feito",E18&lt;&gt;"",F18&lt;&gt;""),F18-E18,"")</f>
         <v/>
@@ -2387,8 +3052,8 @@
       <c r="B19" s="17" t="n"/>
       <c r="C19" s="17" t="n"/>
       <c r="D19" s="17" t="n"/>
-      <c r="E19" s="20" t="n"/>
-      <c r="F19" s="20" t="n"/>
+      <c r="E19" s="30" t="n"/>
+      <c r="F19" s="30" t="n"/>
       <c r="G19" s="17">
         <f>IF(AND(D19="Feito",E19&lt;&gt;"",F19&lt;&gt;""),F19-E19,"")</f>
         <v/>
@@ -2410,8 +3075,8 @@
       <c r="B20" s="17" t="n"/>
       <c r="C20" s="17" t="n"/>
       <c r="D20" s="17" t="n"/>
-      <c r="E20" s="20" t="n"/>
-      <c r="F20" s="20" t="n"/>
+      <c r="E20" s="30" t="n"/>
+      <c r="F20" s="30" t="n"/>
       <c r="G20" s="17">
         <f>IF(AND(D20="Feito",E20&lt;&gt;"",F20&lt;&gt;""),F20-E20,"")</f>
         <v/>
@@ -2433,8 +3098,8 @@
       <c r="B21" s="17" t="n"/>
       <c r="C21" s="17" t="n"/>
       <c r="D21" s="17" t="n"/>
-      <c r="E21" s="20" t="n"/>
-      <c r="F21" s="20" t="n"/>
+      <c r="E21" s="30" t="n"/>
+      <c r="F21" s="30" t="n"/>
       <c r="G21" s="17">
         <f>IF(AND(D21="Feito",E21&lt;&gt;"",F21&lt;&gt;""),F21-E21,"")</f>
         <v/>
@@ -2456,8 +3121,8 @@
       <c r="B22" s="17" t="n"/>
       <c r="C22" s="17" t="n"/>
       <c r="D22" s="17" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="20" t="n"/>
+      <c r="E22" s="30" t="n"/>
+      <c r="F22" s="30" t="n"/>
       <c r="G22" s="17">
         <f>IF(AND(D22="Feito",E22&lt;&gt;"",F22&lt;&gt;""),F22-E22,"")</f>
         <v/>
@@ -2479,8 +3144,8 @@
       <c r="B23" s="17" t="n"/>
       <c r="C23" s="17" t="n"/>
       <c r="D23" s="17" t="n"/>
-      <c r="E23" s="20" t="n"/>
-      <c r="F23" s="20" t="n"/>
+      <c r="E23" s="30" t="n"/>
+      <c r="F23" s="30" t="n"/>
       <c r="G23" s="17">
         <f>IF(AND(D23="Feito",E23&lt;&gt;"",F23&lt;&gt;""),F23-E23,"")</f>
         <v/>
@@ -2502,8 +3167,8 @@
       <c r="B24" s="17" t="n"/>
       <c r="C24" s="17" t="n"/>
       <c r="D24" s="17" t="n"/>
-      <c r="E24" s="20" t="n"/>
-      <c r="F24" s="20" t="n"/>
+      <c r="E24" s="30" t="n"/>
+      <c r="F24" s="30" t="n"/>
       <c r="G24" s="17">
         <f>IF(AND(D24="Feito",E24&lt;&gt;"",F24&lt;&gt;""),F24-E24,"")</f>
         <v/>
@@ -2525,8 +3190,8 @@
       <c r="B25" s="17" t="n"/>
       <c r="C25" s="17" t="n"/>
       <c r="D25" s="17" t="n"/>
-      <c r="E25" s="20" t="n"/>
-      <c r="F25" s="20" t="n"/>
+      <c r="E25" s="30" t="n"/>
+      <c r="F25" s="30" t="n"/>
       <c r="G25" s="17">
         <f>IF(AND(D25="Feito",E25&lt;&gt;"",F25&lt;&gt;""),F25-E25,"")</f>
         <v/>
@@ -2548,8 +3213,8 @@
       <c r="B26" s="17" t="n"/>
       <c r="C26" s="17" t="n"/>
       <c r="D26" s="17" t="n"/>
-      <c r="E26" s="20" t="n"/>
-      <c r="F26" s="20" t="n"/>
+      <c r="E26" s="30" t="n"/>
+      <c r="F26" s="30" t="n"/>
       <c r="G26" s="17">
         <f>IF(AND(D26="Feito",E26&lt;&gt;"",F26&lt;&gt;""),F26-E26,"")</f>
         <v/>
@@ -2571,8 +3236,8 @@
       <c r="B27" s="17" t="n"/>
       <c r="C27" s="17" t="n"/>
       <c r="D27" s="17" t="n"/>
-      <c r="E27" s="20" t="n"/>
-      <c r="F27" s="20" t="n"/>
+      <c r="E27" s="30" t="n"/>
+      <c r="F27" s="30" t="n"/>
       <c r="G27" s="17">
         <f>IF(AND(D27="Feito",E27&lt;&gt;"",F27&lt;&gt;""),F27-E27,"")</f>
         <v/>
@@ -2594,8 +3259,8 @@
       <c r="B28" s="17" t="n"/>
       <c r="C28" s="17" t="n"/>
       <c r="D28" s="17" t="n"/>
-      <c r="E28" s="20" t="n"/>
-      <c r="F28" s="20" t="n"/>
+      <c r="E28" s="30" t="n"/>
+      <c r="F28" s="30" t="n"/>
       <c r="G28" s="17">
         <f>IF(AND(D28="Feito",E28&lt;&gt;"",F28&lt;&gt;""),F28-E28,"")</f>
         <v/>
@@ -2617,8 +3282,8 @@
       <c r="B29" s="17" t="n"/>
       <c r="C29" s="17" t="n"/>
       <c r="D29" s="17" t="n"/>
-      <c r="E29" s="20" t="n"/>
-      <c r="F29" s="20" t="n"/>
+      <c r="E29" s="30" t="n"/>
+      <c r="F29" s="30" t="n"/>
       <c r="G29" s="17">
         <f>IF(AND(D29="Feito",E29&lt;&gt;"",F29&lt;&gt;""),F29-E29,"")</f>
         <v/>
@@ -2640,8 +3305,8 @@
       <c r="B30" s="17" t="n"/>
       <c r="C30" s="17" t="n"/>
       <c r="D30" s="17" t="n"/>
-      <c r="E30" s="20" t="n"/>
-      <c r="F30" s="20" t="n"/>
+      <c r="E30" s="30" t="n"/>
+      <c r="F30" s="30" t="n"/>
       <c r="G30" s="17">
         <f>IF(AND(D30="Feito",E30&lt;&gt;"",F30&lt;&gt;""),F30-E30,"")</f>
         <v/>
@@ -2663,8 +3328,8 @@
       <c r="B31" s="17" t="n"/>
       <c r="C31" s="17" t="n"/>
       <c r="D31" s="17" t="n"/>
-      <c r="E31" s="20" t="n"/>
-      <c r="F31" s="20" t="n"/>
+      <c r="E31" s="30" t="n"/>
+      <c r="F31" s="30" t="n"/>
       <c r="G31" s="17">
         <f>IF(AND(D31="Feito",E31&lt;&gt;"",F31&lt;&gt;""),F31-E31,"")</f>
         <v/>
@@ -2686,8 +3351,8 @@
       <c r="B32" s="17" t="n"/>
       <c r="C32" s="17" t="n"/>
       <c r="D32" s="17" t="n"/>
-      <c r="E32" s="20" t="n"/>
-      <c r="F32" s="20" t="n"/>
+      <c r="E32" s="30" t="n"/>
+      <c r="F32" s="30" t="n"/>
       <c r="G32" s="17">
         <f>IF(AND(D32="Feito",E32&lt;&gt;"",F32&lt;&gt;""),F32-E32,"")</f>
         <v/>
@@ -2709,8 +3374,8 @@
       <c r="B33" s="17" t="n"/>
       <c r="C33" s="17" t="n"/>
       <c r="D33" s="17" t="n"/>
-      <c r="E33" s="20" t="n"/>
-      <c r="F33" s="20" t="n"/>
+      <c r="E33" s="30" t="n"/>
+      <c r="F33" s="30" t="n"/>
       <c r="G33" s="17">
         <f>IF(AND(D33="Feito",E33&lt;&gt;"",F33&lt;&gt;""),F33-E33,"")</f>
         <v/>
@@ -2732,8 +3397,8 @@
       <c r="B34" s="17" t="n"/>
       <c r="C34" s="17" t="n"/>
       <c r="D34" s="17" t="n"/>
-      <c r="E34" s="20" t="n"/>
-      <c r="F34" s="20" t="n"/>
+      <c r="E34" s="30" t="n"/>
+      <c r="F34" s="30" t="n"/>
       <c r="G34" s="17">
         <f>IF(AND(D34="Feito",E34&lt;&gt;"",F34&lt;&gt;""),F34-E34,"")</f>
         <v/>
@@ -2755,8 +3420,8 @@
       <c r="B35" s="17" t="n"/>
       <c r="C35" s="17" t="n"/>
       <c r="D35" s="17" t="n"/>
-      <c r="E35" s="20" t="n"/>
-      <c r="F35" s="20" t="n"/>
+      <c r="E35" s="30" t="n"/>
+      <c r="F35" s="30" t="n"/>
       <c r="G35" s="17">
         <f>IF(AND(D35="Feito",E35&lt;&gt;"",F35&lt;&gt;""),F35-E35,"")</f>
         <v/>
@@ -2778,8 +3443,8 @@
       <c r="B36" s="17" t="n"/>
       <c r="C36" s="17" t="n"/>
       <c r="D36" s="17" t="n"/>
-      <c r="E36" s="20" t="n"/>
-      <c r="F36" s="20" t="n"/>
+      <c r="E36" s="30" t="n"/>
+      <c r="F36" s="30" t="n"/>
       <c r="G36" s="17">
         <f>IF(AND(D36="Feito",E36&lt;&gt;"",F36&lt;&gt;""),F36-E36,"")</f>
         <v/>
@@ -2801,8 +3466,8 @@
       <c r="B37" s="17" t="n"/>
       <c r="C37" s="17" t="n"/>
       <c r="D37" s="17" t="n"/>
-      <c r="E37" s="20" t="n"/>
-      <c r="F37" s="20" t="n"/>
+      <c r="E37" s="30" t="n"/>
+      <c r="F37" s="30" t="n"/>
       <c r="G37" s="17">
         <f>IF(AND(D37="Feito",E37&lt;&gt;"",F37&lt;&gt;""),F37-E37,"")</f>
         <v/>
@@ -2824,8 +3489,8 @@
       <c r="B38" s="17" t="n"/>
       <c r="C38" s="17" t="n"/>
       <c r="D38" s="17" t="n"/>
-      <c r="E38" s="20" t="n"/>
-      <c r="F38" s="20" t="n"/>
+      <c r="E38" s="30" t="n"/>
+      <c r="F38" s="30" t="n"/>
       <c r="G38" s="17">
         <f>IF(AND(D38="Feito",E38&lt;&gt;"",F38&lt;&gt;""),F38-E38,"")</f>
         <v/>
@@ -2847,8 +3512,8 @@
       <c r="B39" s="17" t="n"/>
       <c r="C39" s="17" t="n"/>
       <c r="D39" s="17" t="n"/>
-      <c r="E39" s="20" t="n"/>
-      <c r="F39" s="20" t="n"/>
+      <c r="E39" s="30" t="n"/>
+      <c r="F39" s="30" t="n"/>
       <c r="G39" s="17">
         <f>IF(AND(D39="Feito",E39&lt;&gt;"",F39&lt;&gt;""),F39-E39,"")</f>
         <v/>
@@ -2870,8 +3535,8 @@
       <c r="B40" s="17" t="n"/>
       <c r="C40" s="17" t="n"/>
       <c r="D40" s="17" t="n"/>
-      <c r="E40" s="20" t="n"/>
-      <c r="F40" s="20" t="n"/>
+      <c r="E40" s="30" t="n"/>
+      <c r="F40" s="30" t="n"/>
       <c r="G40" s="17">
         <f>IF(AND(D40="Feito",E40&lt;&gt;"",F40&lt;&gt;""),F40-E40,"")</f>
         <v/>
@@ -2893,8 +3558,8 @@
       <c r="B41" s="17" t="n"/>
       <c r="C41" s="17" t="n"/>
       <c r="D41" s="17" t="n"/>
-      <c r="E41" s="20" t="n"/>
-      <c r="F41" s="20" t="n"/>
+      <c r="E41" s="30" t="n"/>
+      <c r="F41" s="30" t="n"/>
       <c r="G41" s="17">
         <f>IF(AND(D41="Feito",E41&lt;&gt;"",F41&lt;&gt;""),F41-E41,"")</f>
         <v/>
@@ -2916,8 +3581,8 @@
       <c r="B42" s="17" t="n"/>
       <c r="C42" s="17" t="n"/>
       <c r="D42" s="17" t="n"/>
-      <c r="E42" s="20" t="n"/>
-      <c r="F42" s="20" t="n"/>
+      <c r="E42" s="30" t="n"/>
+      <c r="F42" s="30" t="n"/>
       <c r="G42" s="17">
         <f>IF(AND(D42="Feito",E42&lt;&gt;"",F42&lt;&gt;""),F42-E42,"")</f>
         <v/>
@@ -2939,8 +3604,8 @@
       <c r="B43" s="17" t="n"/>
       <c r="C43" s="17" t="n"/>
       <c r="D43" s="17" t="n"/>
-      <c r="E43" s="20" t="n"/>
-      <c r="F43" s="20" t="n"/>
+      <c r="E43" s="30" t="n"/>
+      <c r="F43" s="30" t="n"/>
       <c r="G43" s="17">
         <f>IF(AND(D43="Feito",E43&lt;&gt;"",F43&lt;&gt;""),F43-E43,"")</f>
         <v/>
@@ -2962,8 +3627,8 @@
       <c r="B44" s="17" t="n"/>
       <c r="C44" s="17" t="n"/>
       <c r="D44" s="17" t="n"/>
-      <c r="E44" s="20" t="n"/>
-      <c r="F44" s="20" t="n"/>
+      <c r="E44" s="30" t="n"/>
+      <c r="F44" s="30" t="n"/>
       <c r="G44" s="17">
         <f>IF(AND(D44="Feito",E44&lt;&gt;"",F44&lt;&gt;""),F44-E44,"")</f>
         <v/>
@@ -2985,8 +3650,8 @@
       <c r="B45" s="17" t="n"/>
       <c r="C45" s="17" t="n"/>
       <c r="D45" s="17" t="n"/>
-      <c r="E45" s="20" t="n"/>
-      <c r="F45" s="20" t="n"/>
+      <c r="E45" s="30" t="n"/>
+      <c r="F45" s="30" t="n"/>
       <c r="G45" s="17">
         <f>IF(AND(D45="Feito",E45&lt;&gt;"",F45&lt;&gt;""),F45-E45,"")</f>
         <v/>
@@ -3008,8 +3673,8 @@
       <c r="B46" s="17" t="n"/>
       <c r="C46" s="17" t="n"/>
       <c r="D46" s="17" t="n"/>
-      <c r="E46" s="20" t="n"/>
-      <c r="F46" s="20" t="n"/>
+      <c r="E46" s="30" t="n"/>
+      <c r="F46" s="30" t="n"/>
       <c r="G46" s="17">
         <f>IF(AND(D46="Feito",E46&lt;&gt;"",F46&lt;&gt;""),F46-E46,"")</f>
         <v/>
@@ -3031,8 +3696,8 @@
       <c r="B47" s="17" t="n"/>
       <c r="C47" s="17" t="n"/>
       <c r="D47" s="17" t="n"/>
-      <c r="E47" s="20" t="n"/>
-      <c r="F47" s="20" t="n"/>
+      <c r="E47" s="30" t="n"/>
+      <c r="F47" s="30" t="n"/>
       <c r="G47" s="17">
         <f>IF(AND(D47="Feito",E47&lt;&gt;"",F47&lt;&gt;""),F47-E47,"")</f>
         <v/>
@@ -3054,8 +3719,8 @@
       <c r="B48" s="17" t="n"/>
       <c r="C48" s="17" t="n"/>
       <c r="D48" s="17" t="n"/>
-      <c r="E48" s="20" t="n"/>
-      <c r="F48" s="20" t="n"/>
+      <c r="E48" s="30" t="n"/>
+      <c r="F48" s="30" t="n"/>
       <c r="G48" s="17">
         <f>IF(AND(D48="Feito",E48&lt;&gt;"",F48&lt;&gt;""),F48-E48,"")</f>
         <v/>
@@ -3077,8 +3742,8 @@
       <c r="B49" s="17" t="n"/>
       <c r="C49" s="17" t="n"/>
       <c r="D49" s="17" t="n"/>
-      <c r="E49" s="20" t="n"/>
-      <c r="F49" s="20" t="n"/>
+      <c r="E49" s="30" t="n"/>
+      <c r="F49" s="30" t="n"/>
       <c r="G49" s="17">
         <f>IF(AND(D49="Feito",E49&lt;&gt;"",F49&lt;&gt;""),F49-E49,"")</f>
         <v/>
@@ -3100,8 +3765,8 @@
       <c r="B50" s="17" t="n"/>
       <c r="C50" s="17" t="n"/>
       <c r="D50" s="17" t="n"/>
-      <c r="E50" s="20" t="n"/>
-      <c r="F50" s="20" t="n"/>
+      <c r="E50" s="30" t="n"/>
+      <c r="F50" s="30" t="n"/>
       <c r="G50" s="17">
         <f>IF(AND(D50="Feito",E50&lt;&gt;"",F50&lt;&gt;""),F50-E50,"")</f>
         <v/>
@@ -3123,8 +3788,8 @@
       <c r="B51" s="17" t="n"/>
       <c r="C51" s="17" t="n"/>
       <c r="D51" s="17" t="n"/>
-      <c r="E51" s="20" t="n"/>
-      <c r="F51" s="20" t="n"/>
+      <c r="E51" s="30" t="n"/>
+      <c r="F51" s="30" t="n"/>
       <c r="G51" s="17">
         <f>IF(AND(D51="Feito",E51&lt;&gt;"",F51&lt;&gt;""),F51-E51,"")</f>
         <v/>
@@ -3146,8 +3811,8 @@
       <c r="B52" s="17" t="n"/>
       <c r="C52" s="17" t="n"/>
       <c r="D52" s="17" t="n"/>
-      <c r="E52" s="20" t="n"/>
-      <c r="F52" s="20" t="n"/>
+      <c r="E52" s="30" t="n"/>
+      <c r="F52" s="30" t="n"/>
       <c r="G52" s="17">
         <f>IF(AND(D52="Feito",E52&lt;&gt;"",F52&lt;&gt;""),F52-E52,"")</f>
         <v/>
@@ -3169,8 +3834,8 @@
       <c r="B53" s="17" t="n"/>
       <c r="C53" s="17" t="n"/>
       <c r="D53" s="17" t="n"/>
-      <c r="E53" s="20" t="n"/>
-      <c r="F53" s="20" t="n"/>
+      <c r="E53" s="30" t="n"/>
+      <c r="F53" s="30" t="n"/>
       <c r="G53" s="17">
         <f>IF(AND(D53="Feito",E53&lt;&gt;"",F53&lt;&gt;""),F53-E53,"")</f>
         <v/>
@@ -3192,8 +3857,8 @@
       <c r="B54" s="17" t="n"/>
       <c r="C54" s="17" t="n"/>
       <c r="D54" s="17" t="n"/>
-      <c r="E54" s="20" t="n"/>
-      <c r="F54" s="20" t="n"/>
+      <c r="E54" s="30" t="n"/>
+      <c r="F54" s="30" t="n"/>
       <c r="G54" s="17">
         <f>IF(AND(D54="Feito",E54&lt;&gt;"",F54&lt;&gt;""),F54-E54,"")</f>
         <v/>
@@ -3215,8 +3880,8 @@
       <c r="B55" s="17" t="n"/>
       <c r="C55" s="17" t="n"/>
       <c r="D55" s="17" t="n"/>
-      <c r="E55" s="20" t="n"/>
-      <c r="F55" s="20" t="n"/>
+      <c r="E55" s="30" t="n"/>
+      <c r="F55" s="30" t="n"/>
       <c r="G55" s="17">
         <f>IF(AND(D55="Feito",E55&lt;&gt;"",F55&lt;&gt;""),F55-E55,"")</f>
         <v/>
@@ -3238,8 +3903,8 @@
       <c r="B56" s="17" t="n"/>
       <c r="C56" s="17" t="n"/>
       <c r="D56" s="17" t="n"/>
-      <c r="E56" s="20" t="n"/>
-      <c r="F56" s="20" t="n"/>
+      <c r="E56" s="30" t="n"/>
+      <c r="F56" s="30" t="n"/>
       <c r="G56" s="17">
         <f>IF(AND(D56="Feito",E56&lt;&gt;"",F56&lt;&gt;""),F56-E56,"")</f>
         <v/>
@@ -3261,8 +3926,8 @@
       <c r="B57" s="17" t="n"/>
       <c r="C57" s="17" t="n"/>
       <c r="D57" s="17" t="n"/>
-      <c r="E57" s="20" t="n"/>
-      <c r="F57" s="20" t="n"/>
+      <c r="E57" s="30" t="n"/>
+      <c r="F57" s="30" t="n"/>
       <c r="G57" s="17">
         <f>IF(AND(D57="Feito",E57&lt;&gt;"",F57&lt;&gt;""),F57-E57,"")</f>
         <v/>
@@ -3284,8 +3949,8 @@
       <c r="B58" s="17" t="n"/>
       <c r="C58" s="17" t="n"/>
       <c r="D58" s="17" t="n"/>
-      <c r="E58" s="20" t="n"/>
-      <c r="F58" s="20" t="n"/>
+      <c r="E58" s="30" t="n"/>
+      <c r="F58" s="30" t="n"/>
       <c r="G58" s="17">
         <f>IF(AND(D58="Feito",E58&lt;&gt;"",F58&lt;&gt;""),F58-E58,"")</f>
         <v/>
@@ -3307,8 +3972,8 @@
       <c r="B59" s="17" t="n"/>
       <c r="C59" s="17" t="n"/>
       <c r="D59" s="17" t="n"/>
-      <c r="E59" s="20" t="n"/>
-      <c r="F59" s="20" t="n"/>
+      <c r="E59" s="30" t="n"/>
+      <c r="F59" s="30" t="n"/>
       <c r="G59" s="17">
         <f>IF(AND(D59="Feito",E59&lt;&gt;"",F59&lt;&gt;""),F59-E59,"")</f>
         <v/>
@@ -3330,8 +3995,8 @@
       <c r="B60" s="17" t="n"/>
       <c r="C60" s="17" t="n"/>
       <c r="D60" s="17" t="n"/>
-      <c r="E60" s="20" t="n"/>
-      <c r="F60" s="20" t="n"/>
+      <c r="E60" s="30" t="n"/>
+      <c r="F60" s="30" t="n"/>
       <c r="G60" s="17">
         <f>IF(AND(D60="Feito",E60&lt;&gt;"",F60&lt;&gt;""),F60-E60,"")</f>
         <v/>
@@ -3353,8 +4018,8 @@
       <c r="B61" s="17" t="n"/>
       <c r="C61" s="17" t="n"/>
       <c r="D61" s="17" t="n"/>
-      <c r="E61" s="20" t="n"/>
-      <c r="F61" s="20" t="n"/>
+      <c r="E61" s="30" t="n"/>
+      <c r="F61" s="30" t="n"/>
       <c r="G61" s="17">
         <f>IF(AND(D61="Feito",E61&lt;&gt;"",F61&lt;&gt;""),F61-E61,"")</f>
         <v/>
@@ -3376,8 +4041,8 @@
       <c r="B62" s="17" t="n"/>
       <c r="C62" s="17" t="n"/>
       <c r="D62" s="17" t="n"/>
-      <c r="E62" s="20" t="n"/>
-      <c r="F62" s="20" t="n"/>
+      <c r="E62" s="30" t="n"/>
+      <c r="F62" s="30" t="n"/>
       <c r="G62" s="17">
         <f>IF(AND(D62="Feito",E62&lt;&gt;"",F62&lt;&gt;""),F62-E62,"")</f>
         <v/>
@@ -3399,8 +4064,8 @@
       <c r="B63" s="17" t="n"/>
       <c r="C63" s="17" t="n"/>
       <c r="D63" s="17" t="n"/>
-      <c r="E63" s="20" t="n"/>
-      <c r="F63" s="20" t="n"/>
+      <c r="E63" s="30" t="n"/>
+      <c r="F63" s="30" t="n"/>
       <c r="G63" s="17">
         <f>IF(AND(D63="Feito",E63&lt;&gt;"",F63&lt;&gt;""),F63-E63,"")</f>
         <v/>
@@ -3422,8 +4087,8 @@
       <c r="B64" s="17" t="n"/>
       <c r="C64" s="17" t="n"/>
       <c r="D64" s="17" t="n"/>
-      <c r="E64" s="20" t="n"/>
-      <c r="F64" s="20" t="n"/>
+      <c r="E64" s="30" t="n"/>
+      <c r="F64" s="30" t="n"/>
       <c r="G64" s="17">
         <f>IF(AND(D64="Feito",E64&lt;&gt;"",F64&lt;&gt;""),F64-E64,"")</f>
         <v/>
@@ -3445,8 +4110,8 @@
       <c r="B65" s="17" t="n"/>
       <c r="C65" s="17" t="n"/>
       <c r="D65" s="17" t="n"/>
-      <c r="E65" s="20" t="n"/>
-      <c r="F65" s="20" t="n"/>
+      <c r="E65" s="30" t="n"/>
+      <c r="F65" s="30" t="n"/>
       <c r="G65" s="17">
         <f>IF(AND(D65="Feito",E65&lt;&gt;"",F65&lt;&gt;""),F65-E65,"")</f>
         <v/>
@@ -3468,8 +4133,8 @@
       <c r="B66" s="17" t="n"/>
       <c r="C66" s="17" t="n"/>
       <c r="D66" s="17" t="n"/>
-      <c r="E66" s="20" t="n"/>
-      <c r="F66" s="20" t="n"/>
+      <c r="E66" s="30" t="n"/>
+      <c r="F66" s="30" t="n"/>
       <c r="G66" s="17">
         <f>IF(AND(D66="Feito",E66&lt;&gt;"",F66&lt;&gt;""),F66-E66,"")</f>
         <v/>
@@ -3491,8 +4156,8 @@
       <c r="B67" s="17" t="n"/>
       <c r="C67" s="17" t="n"/>
       <c r="D67" s="17" t="n"/>
-      <c r="E67" s="20" t="n"/>
-      <c r="F67" s="20" t="n"/>
+      <c r="E67" s="30" t="n"/>
+      <c r="F67" s="30" t="n"/>
       <c r="G67" s="17">
         <f>IF(AND(D67="Feito",E67&lt;&gt;"",F67&lt;&gt;""),F67-E67,"")</f>
         <v/>
@@ -3514,8 +4179,8 @@
       <c r="B68" s="17" t="n"/>
       <c r="C68" s="17" t="n"/>
       <c r="D68" s="17" t="n"/>
-      <c r="E68" s="20" t="n"/>
-      <c r="F68" s="20" t="n"/>
+      <c r="E68" s="30" t="n"/>
+      <c r="F68" s="30" t="n"/>
       <c r="G68" s="17">
         <f>IF(AND(D68="Feito",E68&lt;&gt;"",F68&lt;&gt;""),F68-E68,"")</f>
         <v/>
@@ -3537,8 +4202,8 @@
       <c r="B69" s="17" t="n"/>
       <c r="C69" s="17" t="n"/>
       <c r="D69" s="17" t="n"/>
-      <c r="E69" s="20" t="n"/>
-      <c r="F69" s="20" t="n"/>
+      <c r="E69" s="30" t="n"/>
+      <c r="F69" s="30" t="n"/>
       <c r="G69" s="17">
         <f>IF(AND(D69="Feito",E69&lt;&gt;"",F69&lt;&gt;""),F69-E69,"")</f>
         <v/>
@@ -3560,8 +4225,8 @@
       <c r="B70" s="17" t="n"/>
       <c r="C70" s="17" t="n"/>
       <c r="D70" s="17" t="n"/>
-      <c r="E70" s="20" t="n"/>
-      <c r="F70" s="20" t="n"/>
+      <c r="E70" s="30" t="n"/>
+      <c r="F70" s="30" t="n"/>
       <c r="G70" s="17">
         <f>IF(AND(D70="Feito",E70&lt;&gt;"",F70&lt;&gt;""),F70-E70,"")</f>
         <v/>
@@ -3583,8 +4248,8 @@
       <c r="B71" s="17" t="n"/>
       <c r="C71" s="17" t="n"/>
       <c r="D71" s="17" t="n"/>
-      <c r="E71" s="20" t="n"/>
-      <c r="F71" s="20" t="n"/>
+      <c r="E71" s="30" t="n"/>
+      <c r="F71" s="30" t="n"/>
       <c r="G71" s="17">
         <f>IF(AND(D71="Feito",E71&lt;&gt;"",F71&lt;&gt;""),F71-E71,"")</f>
         <v/>
@@ -3606,8 +4271,8 @@
       <c r="B72" s="17" t="n"/>
       <c r="C72" s="17" t="n"/>
       <c r="D72" s="17" t="n"/>
-      <c r="E72" s="20" t="n"/>
-      <c r="F72" s="20" t="n"/>
+      <c r="E72" s="30" t="n"/>
+      <c r="F72" s="30" t="n"/>
       <c r="G72" s="17">
         <f>IF(AND(D72="Feito",E72&lt;&gt;"",F72&lt;&gt;""),F72-E72,"")</f>
         <v/>
@@ -3629,8 +4294,8 @@
       <c r="B73" s="17" t="n"/>
       <c r="C73" s="17" t="n"/>
       <c r="D73" s="17" t="n"/>
-      <c r="E73" s="20" t="n"/>
-      <c r="F73" s="20" t="n"/>
+      <c r="E73" s="30" t="n"/>
+      <c r="F73" s="30" t="n"/>
       <c r="G73" s="17">
         <f>IF(AND(D73="Feito",E73&lt;&gt;"",F73&lt;&gt;""),F73-E73,"")</f>
         <v/>
@@ -3652,8 +4317,8 @@
       <c r="B74" s="17" t="n"/>
       <c r="C74" s="17" t="n"/>
       <c r="D74" s="17" t="n"/>
-      <c r="E74" s="20" t="n"/>
-      <c r="F74" s="20" t="n"/>
+      <c r="E74" s="30" t="n"/>
+      <c r="F74" s="30" t="n"/>
       <c r="G74" s="17">
         <f>IF(AND(D74="Feito",E74&lt;&gt;"",F74&lt;&gt;""),F74-E74,"")</f>
         <v/>
@@ -3675,8 +4340,8 @@
       <c r="B75" s="17" t="n"/>
       <c r="C75" s="17" t="n"/>
       <c r="D75" s="17" t="n"/>
-      <c r="E75" s="20" t="n"/>
-      <c r="F75" s="20" t="n"/>
+      <c r="E75" s="30" t="n"/>
+      <c r="F75" s="30" t="n"/>
       <c r="G75" s="17">
         <f>IF(AND(D75="Feito",E75&lt;&gt;"",F75&lt;&gt;""),F75-E75,"")</f>
         <v/>
@@ -3698,8 +4363,8 @@
       <c r="B76" s="17" t="n"/>
       <c r="C76" s="17" t="n"/>
       <c r="D76" s="17" t="n"/>
-      <c r="E76" s="20" t="n"/>
-      <c r="F76" s="20" t="n"/>
+      <c r="E76" s="30" t="n"/>
+      <c r="F76" s="30" t="n"/>
       <c r="G76" s="17">
         <f>IF(AND(D76="Feito",E76&lt;&gt;"",F76&lt;&gt;""),F76-E76,"")</f>
         <v/>
@@ -3721,8 +4386,8 @@
       <c r="B77" s="17" t="n"/>
       <c r="C77" s="17" t="n"/>
       <c r="D77" s="17" t="n"/>
-      <c r="E77" s="20" t="n"/>
-      <c r="F77" s="20" t="n"/>
+      <c r="E77" s="30" t="n"/>
+      <c r="F77" s="30" t="n"/>
       <c r="G77" s="17">
         <f>IF(AND(D77="Feito",E77&lt;&gt;"",F77&lt;&gt;""),F77-E77,"")</f>
         <v/>
@@ -3744,8 +4409,8 @@
       <c r="B78" s="17" t="n"/>
       <c r="C78" s="17" t="n"/>
       <c r="D78" s="17" t="n"/>
-      <c r="E78" s="20" t="n"/>
-      <c r="F78" s="20" t="n"/>
+      <c r="E78" s="30" t="n"/>
+      <c r="F78" s="30" t="n"/>
       <c r="G78" s="17">
         <f>IF(AND(D78="Feito",E78&lt;&gt;"",F78&lt;&gt;""),F78-E78,"")</f>
         <v/>
@@ -3767,8 +4432,8 @@
       <c r="B79" s="17" t="n"/>
       <c r="C79" s="17" t="n"/>
       <c r="D79" s="17" t="n"/>
-      <c r="E79" s="20" t="n"/>
-      <c r="F79" s="20" t="n"/>
+      <c r="E79" s="30" t="n"/>
+      <c r="F79" s="30" t="n"/>
       <c r="G79" s="17">
         <f>IF(AND(D79="Feito",E79&lt;&gt;"",F79&lt;&gt;""),F79-E79,"")</f>
         <v/>
@@ -3790,8 +4455,8 @@
       <c r="B80" s="17" t="n"/>
       <c r="C80" s="17" t="n"/>
       <c r="D80" s="17" t="n"/>
-      <c r="E80" s="20" t="n"/>
-      <c r="F80" s="20" t="n"/>
+      <c r="E80" s="30" t="n"/>
+      <c r="F80" s="30" t="n"/>
       <c r="G80" s="17">
         <f>IF(AND(D80="Feito",E80&lt;&gt;"",F80&lt;&gt;""),F80-E80,"")</f>
         <v/>
@@ -3813,8 +4478,8 @@
       <c r="B81" s="17" t="n"/>
       <c r="C81" s="17" t="n"/>
       <c r="D81" s="17" t="n"/>
-      <c r="E81" s="20" t="n"/>
-      <c r="F81" s="20" t="n"/>
+      <c r="E81" s="30" t="n"/>
+      <c r="F81" s="30" t="n"/>
       <c r="G81" s="17">
         <f>IF(AND(D81="Feito",E81&lt;&gt;"",F81&lt;&gt;""),F81-E81,"")</f>
         <v/>
@@ -3836,8 +4501,8 @@
       <c r="B82" s="17" t="n"/>
       <c r="C82" s="17" t="n"/>
       <c r="D82" s="17" t="n"/>
-      <c r="E82" s="20" t="n"/>
-      <c r="F82" s="20" t="n"/>
+      <c r="E82" s="30" t="n"/>
+      <c r="F82" s="30" t="n"/>
       <c r="G82" s="17">
         <f>IF(AND(D82="Feito",E82&lt;&gt;"",F82&lt;&gt;""),F82-E82,"")</f>
         <v/>
@@ -3859,8 +4524,8 @@
       <c r="B83" s="17" t="n"/>
       <c r="C83" s="17" t="n"/>
       <c r="D83" s="17" t="n"/>
-      <c r="E83" s="20" t="n"/>
-      <c r="F83" s="20" t="n"/>
+      <c r="E83" s="30" t="n"/>
+      <c r="F83" s="30" t="n"/>
       <c r="G83" s="17">
         <f>IF(AND(D83="Feito",E83&lt;&gt;"",F83&lt;&gt;""),F83-E83,"")</f>
         <v/>
@@ -3882,8 +4547,8 @@
       <c r="B84" s="17" t="n"/>
       <c r="C84" s="17" t="n"/>
       <c r="D84" s="17" t="n"/>
-      <c r="E84" s="20" t="n"/>
-      <c r="F84" s="20" t="n"/>
+      <c r="E84" s="30" t="n"/>
+      <c r="F84" s="30" t="n"/>
       <c r="G84" s="17">
         <f>IF(AND(D84="Feito",E84&lt;&gt;"",F84&lt;&gt;""),F84-E84,"")</f>
         <v/>
@@ -3905,8 +4570,8 @@
       <c r="B85" s="17" t="n"/>
       <c r="C85" s="17" t="n"/>
       <c r="D85" s="17" t="n"/>
-      <c r="E85" s="20" t="n"/>
-      <c r="F85" s="20" t="n"/>
+      <c r="E85" s="30" t="n"/>
+      <c r="F85" s="30" t="n"/>
       <c r="G85" s="17">
         <f>IF(AND(D85="Feito",E85&lt;&gt;"",F85&lt;&gt;""),F85-E85,"")</f>
         <v/>
@@ -3928,8 +4593,8 @@
       <c r="B86" s="17" t="n"/>
       <c r="C86" s="17" t="n"/>
       <c r="D86" s="17" t="n"/>
-      <c r="E86" s="20" t="n"/>
-      <c r="F86" s="20" t="n"/>
+      <c r="E86" s="30" t="n"/>
+      <c r="F86" s="30" t="n"/>
       <c r="G86" s="17">
         <f>IF(AND(D86="Feito",E86&lt;&gt;"",F86&lt;&gt;""),F86-E86,"")</f>
         <v/>
@@ -3951,8 +4616,8 @@
       <c r="B87" s="17" t="n"/>
       <c r="C87" s="17" t="n"/>
       <c r="D87" s="17" t="n"/>
-      <c r="E87" s="20" t="n"/>
-      <c r="F87" s="20" t="n"/>
+      <c r="E87" s="30" t="n"/>
+      <c r="F87" s="30" t="n"/>
       <c r="G87" s="17">
         <f>IF(AND(D87="Feito",E87&lt;&gt;"",F87&lt;&gt;""),F87-E87,"")</f>
         <v/>
@@ -3974,8 +4639,8 @@
       <c r="B88" s="17" t="n"/>
       <c r="C88" s="17" t="n"/>
       <c r="D88" s="17" t="n"/>
-      <c r="E88" s="20" t="n"/>
-      <c r="F88" s="20" t="n"/>
+      <c r="E88" s="30" t="n"/>
+      <c r="F88" s="30" t="n"/>
       <c r="G88" s="17">
         <f>IF(AND(D88="Feito",E88&lt;&gt;"",F88&lt;&gt;""),F88-E88,"")</f>
         <v/>
@@ -3997,8 +4662,8 @@
       <c r="B89" s="17" t="n"/>
       <c r="C89" s="17" t="n"/>
       <c r="D89" s="17" t="n"/>
-      <c r="E89" s="20" t="n"/>
-      <c r="F89" s="20" t="n"/>
+      <c r="E89" s="30" t="n"/>
+      <c r="F89" s="30" t="n"/>
       <c r="G89" s="17">
         <f>IF(AND(D89="Feito",E89&lt;&gt;"",F89&lt;&gt;""),F89-E89,"")</f>
         <v/>
@@ -4020,8 +4685,8 @@
       <c r="B90" s="17" t="n"/>
       <c r="C90" s="17" t="n"/>
       <c r="D90" s="17" t="n"/>
-      <c r="E90" s="20" t="n"/>
-      <c r="F90" s="20" t="n"/>
+      <c r="E90" s="30" t="n"/>
+      <c r="F90" s="30" t="n"/>
       <c r="G90" s="17">
         <f>IF(AND(D90="Feito",E90&lt;&gt;"",F90&lt;&gt;""),F90-E90,"")</f>
         <v/>
@@ -4043,8 +4708,8 @@
       <c r="B91" s="17" t="n"/>
       <c r="C91" s="17" t="n"/>
       <c r="D91" s="17" t="n"/>
-      <c r="E91" s="20" t="n"/>
-      <c r="F91" s="20" t="n"/>
+      <c r="E91" s="30" t="n"/>
+      <c r="F91" s="30" t="n"/>
       <c r="G91" s="17">
         <f>IF(AND(D91="Feito",E91&lt;&gt;"",F91&lt;&gt;""),F91-E91,"")</f>
         <v/>
@@ -4066,8 +4731,8 @@
       <c r="B92" s="17" t="n"/>
       <c r="C92" s="17" t="n"/>
       <c r="D92" s="17" t="n"/>
-      <c r="E92" s="20" t="n"/>
-      <c r="F92" s="20" t="n"/>
+      <c r="E92" s="30" t="n"/>
+      <c r="F92" s="30" t="n"/>
       <c r="G92" s="17">
         <f>IF(AND(D92="Feito",E92&lt;&gt;"",F92&lt;&gt;""),F92-E92,"")</f>
         <v/>
@@ -4089,8 +4754,8 @@
       <c r="B93" s="17" t="n"/>
       <c r="C93" s="17" t="n"/>
       <c r="D93" s="17" t="n"/>
-      <c r="E93" s="20" t="n"/>
-      <c r="F93" s="20" t="n"/>
+      <c r="E93" s="30" t="n"/>
+      <c r="F93" s="30" t="n"/>
       <c r="G93" s="17">
         <f>IF(AND(D93="Feito",E93&lt;&gt;"",F93&lt;&gt;""),F93-E93,"")</f>
         <v/>
@@ -4112,8 +4777,8 @@
       <c r="B94" s="17" t="n"/>
       <c r="C94" s="17" t="n"/>
       <c r="D94" s="17" t="n"/>
-      <c r="E94" s="20" t="n"/>
-      <c r="F94" s="20" t="n"/>
+      <c r="E94" s="30" t="n"/>
+      <c r="F94" s="30" t="n"/>
       <c r="G94" s="17">
         <f>IF(AND(D94="Feito",E94&lt;&gt;"",F94&lt;&gt;""),F94-E94,"")</f>
         <v/>
@@ -4135,8 +4800,8 @@
       <c r="B95" s="17" t="n"/>
       <c r="C95" s="17" t="n"/>
       <c r="D95" s="17" t="n"/>
-      <c r="E95" s="20" t="n"/>
-      <c r="F95" s="20" t="n"/>
+      <c r="E95" s="30" t="n"/>
+      <c r="F95" s="30" t="n"/>
       <c r="G95" s="17">
         <f>IF(AND(D95="Feito",E95&lt;&gt;"",F95&lt;&gt;""),F95-E95,"")</f>
         <v/>
@@ -4158,8 +4823,8 @@
       <c r="B96" s="17" t="n"/>
       <c r="C96" s="17" t="n"/>
       <c r="D96" s="17" t="n"/>
-      <c r="E96" s="20" t="n"/>
-      <c r="F96" s="20" t="n"/>
+      <c r="E96" s="30" t="n"/>
+      <c r="F96" s="30" t="n"/>
       <c r="G96" s="17">
         <f>IF(AND(D96="Feito",E96&lt;&gt;"",F96&lt;&gt;""),F96-E96,"")</f>
         <v/>
@@ -4181,8 +4846,8 @@
       <c r="B97" s="17" t="n"/>
       <c r="C97" s="17" t="n"/>
       <c r="D97" s="17" t="n"/>
-      <c r="E97" s="20" t="n"/>
-      <c r="F97" s="20" t="n"/>
+      <c r="E97" s="30" t="n"/>
+      <c r="F97" s="30" t="n"/>
       <c r="G97" s="17">
         <f>IF(AND(D97="Feito",E97&lt;&gt;"",F97&lt;&gt;""),F97-E97,"")</f>
         <v/>
@@ -4204,8 +4869,8 @@
       <c r="B98" s="17" t="n"/>
       <c r="C98" s="17" t="n"/>
       <c r="D98" s="17" t="n"/>
-      <c r="E98" s="20" t="n"/>
-      <c r="F98" s="20" t="n"/>
+      <c r="E98" s="30" t="n"/>
+      <c r="F98" s="30" t="n"/>
       <c r="G98" s="17">
         <f>IF(AND(D98="Feito",E98&lt;&gt;"",F98&lt;&gt;""),F98-E98,"")</f>
         <v/>
@@ -4227,8 +4892,8 @@
       <c r="B99" s="17" t="n"/>
       <c r="C99" s="17" t="n"/>
       <c r="D99" s="17" t="n"/>
-      <c r="E99" s="20" t="n"/>
-      <c r="F99" s="20" t="n"/>
+      <c r="E99" s="30" t="n"/>
+      <c r="F99" s="30" t="n"/>
       <c r="G99" s="17">
         <f>IF(AND(D99="Feito",E99&lt;&gt;"",F99&lt;&gt;""),F99-E99,"")</f>
         <v/>
@@ -4250,8 +4915,8 @@
       <c r="B100" s="17" t="n"/>
       <c r="C100" s="17" t="n"/>
       <c r="D100" s="17" t="n"/>
-      <c r="E100" s="20" t="n"/>
-      <c r="F100" s="20" t="n"/>
+      <c r="E100" s="30" t="n"/>
+      <c r="F100" s="30" t="n"/>
       <c r="G100" s="17">
         <f>IF(AND(D100="Feito",E100&lt;&gt;"",F100&lt;&gt;""),F100-E100,"")</f>
         <v/>
@@ -4273,8 +4938,8 @@
       <c r="B101" s="17" t="n"/>
       <c r="C101" s="17" t="n"/>
       <c r="D101" s="17" t="n"/>
-      <c r="E101" s="20" t="n"/>
-      <c r="F101" s="20" t="n"/>
+      <c r="E101" s="30" t="n"/>
+      <c r="F101" s="30" t="n"/>
       <c r="G101" s="17">
         <f>IF(AND(D101="Feito",E101&lt;&gt;"",F101&lt;&gt;""),F101-E101,"")</f>
         <v/>
@@ -4296,8 +4961,8 @@
       <c r="B102" s="17" t="n"/>
       <c r="C102" s="17" t="n"/>
       <c r="D102" s="17" t="n"/>
-      <c r="E102" s="20" t="n"/>
-      <c r="F102" s="20" t="n"/>
+      <c r="E102" s="30" t="n"/>
+      <c r="F102" s="30" t="n"/>
       <c r="G102" s="17">
         <f>IF(AND(D102="Feito",E102&lt;&gt;"",F102&lt;&gt;""),F102-E102,"")</f>
         <v/>
@@ -4319,8 +4984,8 @@
       <c r="B103" s="17" t="n"/>
       <c r="C103" s="17" t="n"/>
       <c r="D103" s="17" t="n"/>
-      <c r="E103" s="20" t="n"/>
-      <c r="F103" s="20" t="n"/>
+      <c r="E103" s="30" t="n"/>
+      <c r="F103" s="30" t="n"/>
       <c r="G103" s="17">
         <f>IF(AND(D103="Feito",E103&lt;&gt;"",F103&lt;&gt;""),F103-E103,"")</f>
         <v/>
@@ -4342,8 +5007,8 @@
       <c r="B104" s="17" t="n"/>
       <c r="C104" s="17" t="n"/>
       <c r="D104" s="17" t="n"/>
-      <c r="E104" s="20" t="n"/>
-      <c r="F104" s="20" t="n"/>
+      <c r="E104" s="30" t="n"/>
+      <c r="F104" s="30" t="n"/>
       <c r="G104" s="17">
         <f>IF(AND(D104="Feito",E104&lt;&gt;"",F104&lt;&gt;""),F104-E104,"")</f>
         <v/>
@@ -4365,8 +5030,8 @@
       <c r="B105" s="17" t="n"/>
       <c r="C105" s="17" t="n"/>
       <c r="D105" s="17" t="n"/>
-      <c r="E105" s="20" t="n"/>
-      <c r="F105" s="20" t="n"/>
+      <c r="E105" s="30" t="n"/>
+      <c r="F105" s="30" t="n"/>
       <c r="G105" s="17">
         <f>IF(AND(D105="Feito",E105&lt;&gt;"",F105&lt;&gt;""),F105-E105,"")</f>
         <v/>
@@ -4388,8 +5053,8 @@
       <c r="B106" s="17" t="n"/>
       <c r="C106" s="17" t="n"/>
       <c r="D106" s="17" t="n"/>
-      <c r="E106" s="20" t="n"/>
-      <c r="F106" s="20" t="n"/>
+      <c r="E106" s="30" t="n"/>
+      <c r="F106" s="30" t="n"/>
       <c r="G106" s="17">
         <f>IF(AND(D106="Feito",E106&lt;&gt;"",F106&lt;&gt;""),F106-E106,"")</f>
         <v/>
@@ -4411,8 +5076,8 @@
       <c r="B107" s="17" t="n"/>
       <c r="C107" s="17" t="n"/>
       <c r="D107" s="17" t="n"/>
-      <c r="E107" s="20" t="n"/>
-      <c r="F107" s="20" t="n"/>
+      <c r="E107" s="30" t="n"/>
+      <c r="F107" s="30" t="n"/>
       <c r="G107" s="17">
         <f>IF(AND(D107="Feito",E107&lt;&gt;"",F107&lt;&gt;""),F107-E107,"")</f>
         <v/>
@@ -4434,8 +5099,8 @@
       <c r="B108" s="17" t="n"/>
       <c r="C108" s="17" t="n"/>
       <c r="D108" s="17" t="n"/>
-      <c r="E108" s="20" t="n"/>
-      <c r="F108" s="20" t="n"/>
+      <c r="E108" s="30" t="n"/>
+      <c r="F108" s="30" t="n"/>
       <c r="G108" s="17">
         <f>IF(AND(D108="Feito",E108&lt;&gt;"",F108&lt;&gt;""),F108-E108,"")</f>
         <v/>
@@ -4457,8 +5122,8 @@
       <c r="B109" s="17" t="n"/>
       <c r="C109" s="17" t="n"/>
       <c r="D109" s="17" t="n"/>
-      <c r="E109" s="20" t="n"/>
-      <c r="F109" s="20" t="n"/>
+      <c r="E109" s="30" t="n"/>
+      <c r="F109" s="30" t="n"/>
       <c r="G109" s="17">
         <f>IF(AND(D109="Feito",E109&lt;&gt;"",F109&lt;&gt;""),F109-E109,"")</f>
         <v/>
@@ -4480,8 +5145,8 @@
       <c r="B110" s="17" t="n"/>
       <c r="C110" s="17" t="n"/>
       <c r="D110" s="17" t="n"/>
-      <c r="E110" s="20" t="n"/>
-      <c r="F110" s="20" t="n"/>
+      <c r="E110" s="30" t="n"/>
+      <c r="F110" s="30" t="n"/>
       <c r="G110" s="17">
         <f>IF(AND(D110="Feito",E110&lt;&gt;"",F110&lt;&gt;""),F110-E110,"")</f>
         <v/>
@@ -4503,8 +5168,8 @@
       <c r="B111" s="17" t="n"/>
       <c r="C111" s="17" t="n"/>
       <c r="D111" s="17" t="n"/>
-      <c r="E111" s="20" t="n"/>
-      <c r="F111" s="20" t="n"/>
+      <c r="E111" s="30" t="n"/>
+      <c r="F111" s="30" t="n"/>
       <c r="G111" s="17">
         <f>IF(AND(D111="Feito",E111&lt;&gt;"",F111&lt;&gt;""),F111-E111,"")</f>
         <v/>
@@ -4526,8 +5191,8 @@
       <c r="B112" s="17" t="n"/>
       <c r="C112" s="17" t="n"/>
       <c r="D112" s="17" t="n"/>
-      <c r="E112" s="20" t="n"/>
-      <c r="F112" s="20" t="n"/>
+      <c r="E112" s="30" t="n"/>
+      <c r="F112" s="30" t="n"/>
       <c r="G112" s="17">
         <f>IF(AND(D112="Feito",E112&lt;&gt;"",F112&lt;&gt;""),F112-E112,"")</f>
         <v/>
@@ -4549,8 +5214,8 @@
       <c r="B113" s="17" t="n"/>
       <c r="C113" s="17" t="n"/>
       <c r="D113" s="17" t="n"/>
-      <c r="E113" s="20" t="n"/>
-      <c r="F113" s="20" t="n"/>
+      <c r="E113" s="30" t="n"/>
+      <c r="F113" s="30" t="n"/>
       <c r="G113" s="17">
         <f>IF(AND(D113="Feito",E113&lt;&gt;"",F113&lt;&gt;""),F113-E113,"")</f>
         <v/>
@@ -4572,8 +5237,8 @@
       <c r="B114" s="17" t="n"/>
       <c r="C114" s="17" t="n"/>
       <c r="D114" s="17" t="n"/>
-      <c r="E114" s="20" t="n"/>
-      <c r="F114" s="20" t="n"/>
+      <c r="E114" s="30" t="n"/>
+      <c r="F114" s="30" t="n"/>
       <c r="G114" s="17">
         <f>IF(AND(D114="Feito",E114&lt;&gt;"",F114&lt;&gt;""),F114-E114,"")</f>
         <v/>
@@ -4595,8 +5260,8 @@
       <c r="B115" s="17" t="n"/>
       <c r="C115" s="17" t="n"/>
       <c r="D115" s="17" t="n"/>
-      <c r="E115" s="20" t="n"/>
-      <c r="F115" s="20" t="n"/>
+      <c r="E115" s="30" t="n"/>
+      <c r="F115" s="30" t="n"/>
       <c r="G115" s="17">
         <f>IF(AND(D115="Feito",E115&lt;&gt;"",F115&lt;&gt;""),F115-E115,"")</f>
         <v/>
@@ -4618,8 +5283,8 @@
       <c r="B116" s="17" t="n"/>
       <c r="C116" s="17" t="n"/>
       <c r="D116" s="17" t="n"/>
-      <c r="E116" s="20" t="n"/>
-      <c r="F116" s="20" t="n"/>
+      <c r="E116" s="30" t="n"/>
+      <c r="F116" s="30" t="n"/>
       <c r="G116" s="17">
         <f>IF(AND(D116="Feito",E116&lt;&gt;"",F116&lt;&gt;""),F116-E116,"")</f>
         <v/>
@@ -4641,8 +5306,8 @@
       <c r="B117" s="17" t="n"/>
       <c r="C117" s="17" t="n"/>
       <c r="D117" s="17" t="n"/>
-      <c r="E117" s="20" t="n"/>
-      <c r="F117" s="20" t="n"/>
+      <c r="E117" s="30" t="n"/>
+      <c r="F117" s="30" t="n"/>
       <c r="G117" s="17">
         <f>IF(AND(D117="Feito",E117&lt;&gt;"",F117&lt;&gt;""),F117-E117,"")</f>
         <v/>
@@ -4664,8 +5329,8 @@
       <c r="B118" s="17" t="n"/>
       <c r="C118" s="17" t="n"/>
       <c r="D118" s="17" t="n"/>
-      <c r="E118" s="20" t="n"/>
-      <c r="F118" s="20" t="n"/>
+      <c r="E118" s="30" t="n"/>
+      <c r="F118" s="30" t="n"/>
       <c r="G118" s="17">
         <f>IF(AND(D118="Feito",E118&lt;&gt;"",F118&lt;&gt;""),F118-E118,"")</f>
         <v/>
@@ -4687,8 +5352,8 @@
       <c r="B119" s="17" t="n"/>
       <c r="C119" s="17" t="n"/>
       <c r="D119" s="17" t="n"/>
-      <c r="E119" s="20" t="n"/>
-      <c r="F119" s="20" t="n"/>
+      <c r="E119" s="30" t="n"/>
+      <c r="F119" s="30" t="n"/>
       <c r="G119" s="17">
         <f>IF(AND(D119="Feito",E119&lt;&gt;"",F119&lt;&gt;""),F119-E119,"")</f>
         <v/>
@@ -4710,8 +5375,8 @@
       <c r="B120" s="17" t="n"/>
       <c r="C120" s="17" t="n"/>
       <c r="D120" s="17" t="n"/>
-      <c r="E120" s="20" t="n"/>
-      <c r="F120" s="20" t="n"/>
+      <c r="E120" s="30" t="n"/>
+      <c r="F120" s="30" t="n"/>
       <c r="G120" s="17">
         <f>IF(AND(D120="Feito",E120&lt;&gt;"",F120&lt;&gt;""),F120-E120,"")</f>
         <v/>
@@ -4733,8 +5398,8 @@
       <c r="B121" s="17" t="n"/>
       <c r="C121" s="17" t="n"/>
       <c r="D121" s="17" t="n"/>
-      <c r="E121" s="20" t="n"/>
-      <c r="F121" s="20" t="n"/>
+      <c r="E121" s="30" t="n"/>
+      <c r="F121" s="30" t="n"/>
       <c r="G121" s="17">
         <f>IF(AND(D121="Feito",E121&lt;&gt;"",F121&lt;&gt;""),F121-E121,"")</f>
         <v/>
@@ -4756,8 +5421,8 @@
       <c r="B122" s="17" t="n"/>
       <c r="C122" s="17" t="n"/>
       <c r="D122" s="17" t="n"/>
-      <c r="E122" s="20" t="n"/>
-      <c r="F122" s="20" t="n"/>
+      <c r="E122" s="30" t="n"/>
+      <c r="F122" s="30" t="n"/>
       <c r="G122" s="17">
         <f>IF(AND(D122="Feito",E122&lt;&gt;"",F122&lt;&gt;""),F122-E122,"")</f>
         <v/>
@@ -4779,8 +5444,8 @@
       <c r="B123" s="17" t="n"/>
       <c r="C123" s="17" t="n"/>
       <c r="D123" s="17" t="n"/>
-      <c r="E123" s="20" t="n"/>
-      <c r="F123" s="20" t="n"/>
+      <c r="E123" s="30" t="n"/>
+      <c r="F123" s="30" t="n"/>
       <c r="G123" s="17">
         <f>IF(AND(D123="Feito",E123&lt;&gt;"",F123&lt;&gt;""),F123-E123,"")</f>
         <v/>
@@ -4802,8 +5467,8 @@
       <c r="B124" s="17" t="n"/>
       <c r="C124" s="17" t="n"/>
       <c r="D124" s="17" t="n"/>
-      <c r="E124" s="20" t="n"/>
-      <c r="F124" s="20" t="n"/>
+      <c r="E124" s="30" t="n"/>
+      <c r="F124" s="30" t="n"/>
       <c r="G124" s="17">
         <f>IF(AND(D124="Feito",E124&lt;&gt;"",F124&lt;&gt;""),F124-E124,"")</f>
         <v/>
@@ -4825,8 +5490,8 @@
       <c r="B125" s="17" t="n"/>
       <c r="C125" s="17" t="n"/>
       <c r="D125" s="17" t="n"/>
-      <c r="E125" s="20" t="n"/>
-      <c r="F125" s="20" t="n"/>
+      <c r="E125" s="30" t="n"/>
+      <c r="F125" s="30" t="n"/>
       <c r="G125" s="17">
         <f>IF(AND(D125="Feito",E125&lt;&gt;"",F125&lt;&gt;""),F125-E125,"")</f>
         <v/>
@@ -4848,8 +5513,8 @@
       <c r="B126" s="17" t="n"/>
       <c r="C126" s="17" t="n"/>
       <c r="D126" s="17" t="n"/>
-      <c r="E126" s="20" t="n"/>
-      <c r="F126" s="20" t="n"/>
+      <c r="E126" s="30" t="n"/>
+      <c r="F126" s="30" t="n"/>
       <c r="G126" s="17">
         <f>IF(AND(D126="Feito",E126&lt;&gt;"",F126&lt;&gt;""),F126-E126,"")</f>
         <v/>
@@ -4871,8 +5536,8 @@
       <c r="B127" s="17" t="n"/>
       <c r="C127" s="17" t="n"/>
       <c r="D127" s="17" t="n"/>
-      <c r="E127" s="20" t="n"/>
-      <c r="F127" s="20" t="n"/>
+      <c r="E127" s="30" t="n"/>
+      <c r="F127" s="30" t="n"/>
       <c r="G127" s="17">
         <f>IF(AND(D127="Feito",E127&lt;&gt;"",F127&lt;&gt;""),F127-E127,"")</f>
         <v/>
@@ -4894,8 +5559,8 @@
       <c r="B128" s="17" t="n"/>
       <c r="C128" s="17" t="n"/>
       <c r="D128" s="17" t="n"/>
-      <c r="E128" s="20" t="n"/>
-      <c r="F128" s="20" t="n"/>
+      <c r="E128" s="30" t="n"/>
+      <c r="F128" s="30" t="n"/>
       <c r="G128" s="17">
         <f>IF(AND(D128="Feito",E128&lt;&gt;"",F128&lt;&gt;""),F128-E128,"")</f>
         <v/>
@@ -4917,8 +5582,8 @@
       <c r="B129" s="17" t="n"/>
       <c r="C129" s="17" t="n"/>
       <c r="D129" s="17" t="n"/>
-      <c r="E129" s="20" t="n"/>
-      <c r="F129" s="20" t="n"/>
+      <c r="E129" s="30" t="n"/>
+      <c r="F129" s="30" t="n"/>
       <c r="G129" s="17">
         <f>IF(AND(D129="Feito",E129&lt;&gt;"",F129&lt;&gt;""),F129-E129,"")</f>
         <v/>
@@ -4940,8 +5605,8 @@
       <c r="B130" s="17" t="n"/>
       <c r="C130" s="17" t="n"/>
       <c r="D130" s="17" t="n"/>
-      <c r="E130" s="20" t="n"/>
-      <c r="F130" s="20" t="n"/>
+      <c r="E130" s="30" t="n"/>
+      <c r="F130" s="30" t="n"/>
       <c r="G130" s="17">
         <f>IF(AND(D130="Feito",E130&lt;&gt;"",F130&lt;&gt;""),F130-E130,"")</f>
         <v/>
@@ -4963,8 +5628,8 @@
       <c r="B131" s="17" t="n"/>
       <c r="C131" s="17" t="n"/>
       <c r="D131" s="17" t="n"/>
-      <c r="E131" s="20" t="n"/>
-      <c r="F131" s="20" t="n"/>
+      <c r="E131" s="30" t="n"/>
+      <c r="F131" s="30" t="n"/>
       <c r="G131" s="17">
         <f>IF(AND(D131="Feito",E131&lt;&gt;"",F131&lt;&gt;""),F131-E131,"")</f>
         <v/>
@@ -4986,8 +5651,8 @@
       <c r="B132" s="17" t="n"/>
       <c r="C132" s="17" t="n"/>
       <c r="D132" s="17" t="n"/>
-      <c r="E132" s="20" t="n"/>
-      <c r="F132" s="20" t="n"/>
+      <c r="E132" s="30" t="n"/>
+      <c r="F132" s="30" t="n"/>
       <c r="G132" s="17">
         <f>IF(AND(D132="Feito",E132&lt;&gt;"",F132&lt;&gt;""),F132-E132,"")</f>
         <v/>
@@ -5009,8 +5674,8 @@
       <c r="B133" s="17" t="n"/>
       <c r="C133" s="17" t="n"/>
       <c r="D133" s="17" t="n"/>
-      <c r="E133" s="20" t="n"/>
-      <c r="F133" s="20" t="n"/>
+      <c r="E133" s="30" t="n"/>
+      <c r="F133" s="30" t="n"/>
       <c r="G133" s="17">
         <f>IF(AND(D133="Feito",E133&lt;&gt;"",F133&lt;&gt;""),F133-E133,"")</f>
         <v/>
@@ -5032,8 +5697,8 @@
       <c r="B134" s="17" t="n"/>
       <c r="C134" s="17" t="n"/>
       <c r="D134" s="17" t="n"/>
-      <c r="E134" s="20" t="n"/>
-      <c r="F134" s="20" t="n"/>
+      <c r="E134" s="30" t="n"/>
+      <c r="F134" s="30" t="n"/>
       <c r="G134" s="17">
         <f>IF(AND(D134="Feito",E134&lt;&gt;"",F134&lt;&gt;""),F134-E134,"")</f>
         <v/>
@@ -5055,8 +5720,8 @@
       <c r="B135" s="17" t="n"/>
       <c r="C135" s="17" t="n"/>
       <c r="D135" s="17" t="n"/>
-      <c r="E135" s="20" t="n"/>
-      <c r="F135" s="20" t="n"/>
+      <c r="E135" s="30" t="n"/>
+      <c r="F135" s="30" t="n"/>
       <c r="G135" s="17">
         <f>IF(AND(D135="Feito",E135&lt;&gt;"",F135&lt;&gt;""),F135-E135,"")</f>
         <v/>
@@ -5078,8 +5743,8 @@
       <c r="B136" s="17" t="n"/>
       <c r="C136" s="17" t="n"/>
       <c r="D136" s="17" t="n"/>
-      <c r="E136" s="20" t="n"/>
-      <c r="F136" s="20" t="n"/>
+      <c r="E136" s="30" t="n"/>
+      <c r="F136" s="30" t="n"/>
       <c r="G136" s="17">
         <f>IF(AND(D136="Feito",E136&lt;&gt;"",F136&lt;&gt;""),F136-E136,"")</f>
         <v/>
@@ -5101,8 +5766,8 @@
       <c r="B137" s="17" t="n"/>
       <c r="C137" s="17" t="n"/>
       <c r="D137" s="17" t="n"/>
-      <c r="E137" s="20" t="n"/>
-      <c r="F137" s="20" t="n"/>
+      <c r="E137" s="30" t="n"/>
+      <c r="F137" s="30" t="n"/>
       <c r="G137" s="17">
         <f>IF(AND(D137="Feito",E137&lt;&gt;"",F137&lt;&gt;""),F137-E137,"")</f>
         <v/>
@@ -5124,8 +5789,8 @@
       <c r="B138" s="17" t="n"/>
       <c r="C138" s="17" t="n"/>
       <c r="D138" s="17" t="n"/>
-      <c r="E138" s="20" t="n"/>
-      <c r="F138" s="20" t="n"/>
+      <c r="E138" s="30" t="n"/>
+      <c r="F138" s="30" t="n"/>
       <c r="G138" s="17">
         <f>IF(AND(D138="Feito",E138&lt;&gt;"",F138&lt;&gt;""),F138-E138,"")</f>
         <v/>
@@ -5147,8 +5812,8 @@
       <c r="B139" s="17" t="n"/>
       <c r="C139" s="17" t="n"/>
       <c r="D139" s="17" t="n"/>
-      <c r="E139" s="20" t="n"/>
-      <c r="F139" s="20" t="n"/>
+      <c r="E139" s="30" t="n"/>
+      <c r="F139" s="30" t="n"/>
       <c r="G139" s="17">
         <f>IF(AND(D139="Feito",E139&lt;&gt;"",F139&lt;&gt;""),F139-E139,"")</f>
         <v/>
@@ -5170,8 +5835,8 @@
       <c r="B140" s="17" t="n"/>
       <c r="C140" s="17" t="n"/>
       <c r="D140" s="17" t="n"/>
-      <c r="E140" s="20" t="n"/>
-      <c r="F140" s="20" t="n"/>
+      <c r="E140" s="30" t="n"/>
+      <c r="F140" s="30" t="n"/>
       <c r="G140" s="17">
         <f>IF(AND(D140="Feito",E140&lt;&gt;"",F140&lt;&gt;""),F140-E140,"")</f>
         <v/>
@@ -5193,8 +5858,8 @@
       <c r="B141" s="17" t="n"/>
       <c r="C141" s="17" t="n"/>
       <c r="D141" s="17" t="n"/>
-      <c r="E141" s="20" t="n"/>
-      <c r="F141" s="20" t="n"/>
+      <c r="E141" s="30" t="n"/>
+      <c r="F141" s="30" t="n"/>
       <c r="G141" s="17">
         <f>IF(AND(D141="Feito",E141&lt;&gt;"",F141&lt;&gt;""),F141-E141,"")</f>
         <v/>
@@ -5216,8 +5881,8 @@
       <c r="B142" s="17" t="n"/>
       <c r="C142" s="17" t="n"/>
       <c r="D142" s="17" t="n"/>
-      <c r="E142" s="20" t="n"/>
-      <c r="F142" s="20" t="n"/>
+      <c r="E142" s="30" t="n"/>
+      <c r="F142" s="30" t="n"/>
       <c r="G142" s="17">
         <f>IF(AND(D142="Feito",E142&lt;&gt;"",F142&lt;&gt;""),F142-E142,"")</f>
         <v/>
@@ -5239,8 +5904,8 @@
       <c r="B143" s="17" t="n"/>
       <c r="C143" s="17" t="n"/>
       <c r="D143" s="17" t="n"/>
-      <c r="E143" s="20" t="n"/>
-      <c r="F143" s="20" t="n"/>
+      <c r="E143" s="30" t="n"/>
+      <c r="F143" s="30" t="n"/>
       <c r="G143" s="17">
         <f>IF(AND(D143="Feito",E143&lt;&gt;"",F143&lt;&gt;""),F143-E143,"")</f>
         <v/>
@@ -5262,8 +5927,8 @@
       <c r="B144" s="17" t="n"/>
       <c r="C144" s="17" t="n"/>
       <c r="D144" s="17" t="n"/>
-      <c r="E144" s="20" t="n"/>
-      <c r="F144" s="20" t="n"/>
+      <c r="E144" s="30" t="n"/>
+      <c r="F144" s="30" t="n"/>
       <c r="G144" s="17">
         <f>IF(AND(D144="Feito",E144&lt;&gt;"",F144&lt;&gt;""),F144-E144,"")</f>
         <v/>
@@ -5285,8 +5950,8 @@
       <c r="B145" s="17" t="n"/>
       <c r="C145" s="17" t="n"/>
       <c r="D145" s="17" t="n"/>
-      <c r="E145" s="20" t="n"/>
-      <c r="F145" s="20" t="n"/>
+      <c r="E145" s="30" t="n"/>
+      <c r="F145" s="30" t="n"/>
       <c r="G145" s="17">
         <f>IF(AND(D145="Feito",E145&lt;&gt;"",F145&lt;&gt;""),F145-E145,"")</f>
         <v/>
@@ -5308,8 +5973,8 @@
       <c r="B146" s="17" t="n"/>
       <c r="C146" s="17" t="n"/>
       <c r="D146" s="17" t="n"/>
-      <c r="E146" s="20" t="n"/>
-      <c r="F146" s="20" t="n"/>
+      <c r="E146" s="30" t="n"/>
+      <c r="F146" s="30" t="n"/>
       <c r="G146" s="17">
         <f>IF(AND(D146="Feito",E146&lt;&gt;"",F146&lt;&gt;""),F146-E146,"")</f>
         <v/>
@@ -5331,8 +5996,8 @@
       <c r="B147" s="17" t="n"/>
       <c r="C147" s="17" t="n"/>
       <c r="D147" s="17" t="n"/>
-      <c r="E147" s="20" t="n"/>
-      <c r="F147" s="20" t="n"/>
+      <c r="E147" s="30" t="n"/>
+      <c r="F147" s="30" t="n"/>
       <c r="G147" s="17">
         <f>IF(AND(D147="Feito",E147&lt;&gt;"",F147&lt;&gt;""),F147-E147,"")</f>
         <v/>
@@ -5354,8 +6019,8 @@
       <c r="B148" s="17" t="n"/>
       <c r="C148" s="17" t="n"/>
       <c r="D148" s="17" t="n"/>
-      <c r="E148" s="20" t="n"/>
-      <c r="F148" s="20" t="n"/>
+      <c r="E148" s="30" t="n"/>
+      <c r="F148" s="30" t="n"/>
       <c r="G148" s="17">
         <f>IF(AND(D148="Feito",E148&lt;&gt;"",F148&lt;&gt;""),F148-E148,"")</f>
         <v/>
@@ -5377,8 +6042,8 @@
       <c r="B149" s="17" t="n"/>
       <c r="C149" s="17" t="n"/>
       <c r="D149" s="17" t="n"/>
-      <c r="E149" s="20" t="n"/>
-      <c r="F149" s="20" t="n"/>
+      <c r="E149" s="30" t="n"/>
+      <c r="F149" s="30" t="n"/>
       <c r="G149" s="17">
         <f>IF(AND(D149="Feito",E149&lt;&gt;"",F149&lt;&gt;""),F149-E149,"")</f>
         <v/>
@@ -5400,8 +6065,8 @@
       <c r="B150" s="17" t="n"/>
       <c r="C150" s="17" t="n"/>
       <c r="D150" s="17" t="n"/>
-      <c r="E150" s="20" t="n"/>
-      <c r="F150" s="20" t="n"/>
+      <c r="E150" s="30" t="n"/>
+      <c r="F150" s="30" t="n"/>
       <c r="G150" s="17">
         <f>IF(AND(D150="Feito",E150&lt;&gt;"",F150&lt;&gt;""),F150-E150,"")</f>
         <v/>
@@ -5423,8 +6088,8 @@
       <c r="B151" s="17" t="n"/>
       <c r="C151" s="17" t="n"/>
       <c r="D151" s="17" t="n"/>
-      <c r="E151" s="20" t="n"/>
-      <c r="F151" s="20" t="n"/>
+      <c r="E151" s="30" t="n"/>
+      <c r="F151" s="30" t="n"/>
       <c r="G151" s="17">
         <f>IF(AND(D151="Feito",E151&lt;&gt;"",F151&lt;&gt;""),F151-E151,"")</f>
         <v/>
@@ -5446,8 +6111,8 @@
       <c r="B152" s="17" t="n"/>
       <c r="C152" s="17" t="n"/>
       <c r="D152" s="17" t="n"/>
-      <c r="E152" s="20" t="n"/>
-      <c r="F152" s="20" t="n"/>
+      <c r="E152" s="30" t="n"/>
+      <c r="F152" s="30" t="n"/>
       <c r="G152" s="17">
         <f>IF(AND(D152="Feito",E152&lt;&gt;"",F152&lt;&gt;""),F152-E152,"")</f>
         <v/>
@@ -5469,8 +6134,8 @@
       <c r="B153" s="17" t="n"/>
       <c r="C153" s="17" t="n"/>
       <c r="D153" s="17" t="n"/>
-      <c r="E153" s="20" t="n"/>
-      <c r="F153" s="20" t="n"/>
+      <c r="E153" s="30" t="n"/>
+      <c r="F153" s="30" t="n"/>
       <c r="G153" s="17">
         <f>IF(AND(D153="Feito",E153&lt;&gt;"",F153&lt;&gt;""),F153-E153,"")</f>
         <v/>
@@ -5492,8 +6157,8 @@
       <c r="B154" s="17" t="n"/>
       <c r="C154" s="17" t="n"/>
       <c r="D154" s="17" t="n"/>
-      <c r="E154" s="20" t="n"/>
-      <c r="F154" s="20" t="n"/>
+      <c r="E154" s="30" t="n"/>
+      <c r="F154" s="30" t="n"/>
       <c r="G154" s="17">
         <f>IF(AND(D154="Feito",E154&lt;&gt;"",F154&lt;&gt;""),F154-E154,"")</f>
         <v/>
@@ -5515,8 +6180,8 @@
       <c r="B155" s="17" t="n"/>
       <c r="C155" s="17" t="n"/>
       <c r="D155" s="17" t="n"/>
-      <c r="E155" s="20" t="n"/>
-      <c r="F155" s="20" t="n"/>
+      <c r="E155" s="30" t="n"/>
+      <c r="F155" s="30" t="n"/>
       <c r="G155" s="17">
         <f>IF(AND(D155="Feito",E155&lt;&gt;"",F155&lt;&gt;""),F155-E155,"")</f>
         <v/>
@@ -5538,8 +6203,8 @@
       <c r="B156" s="17" t="n"/>
       <c r="C156" s="17" t="n"/>
       <c r="D156" s="17" t="n"/>
-      <c r="E156" s="20" t="n"/>
-      <c r="F156" s="20" t="n"/>
+      <c r="E156" s="30" t="n"/>
+      <c r="F156" s="30" t="n"/>
       <c r="G156" s="17">
         <f>IF(AND(D156="Feito",E156&lt;&gt;"",F156&lt;&gt;""),F156-E156,"")</f>
         <v/>
@@ -6191,7 +6856,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I156">
-    <cfRule type="expression" priority="2" dxfId="0">
+    <cfRule type="expression" priority="2" dxfId="2">
       <formula>ISNUMBER(SEARCH("⚠",I6))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6299,15 +6964,15 @@
       <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="33" t="n">
         <v>20</v>
       </c>
       <c r="D6" s="2" t="n"/>
@@ -6317,15 +6982,15 @@
       <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="32" t="n">
         <v>17</v>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="33" t="n">
         <v>18</v>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -6335,15 +7000,15 @@
       <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="33" t="n">
         <v>17</v>
       </c>
       <c r="D8" s="2" t="n"/>
@@ -6353,15 +7018,15 @@
       <c r="H8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="32" t="n">
         <v>11</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="33" t="n">
         <v>13</v>
       </c>
       <c r="D9" s="2" t="n"/>
@@ -6371,15 +7036,15 @@
       <c r="H9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="B10" s="22" t="n">
+      <c r="B10" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="23" t="n">
+      <c r="C10" s="33" t="n">
         <v>11</v>
       </c>
       <c r="D10" s="2" t="n"/>
@@ -6389,15 +7054,15 @@
       <c r="H10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="33" t="n">
         <v>7</v>
       </c>
       <c r="D11" s="2" t="n"/>
@@ -6407,15 +7072,15 @@
       <c r="H11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="33" t="n">
         <v>4</v>
       </c>
       <c r="D12" s="2" t="n"/>
